--- a/ig/DM-JUILLET-2025/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
+++ b/ig/DM-JUILLET-2025/ValueSet-JDV-J157-MomentGlucose-ENS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250425120000</t>
+    <t>20250728120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -145,7 +145,7 @@
     <t>Lors d'un malaise</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/1.2.250.1.213.1.1.4.322</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
   </si>
 </sst>
 </file>
